--- a/downloads/en/proximite-revues.xlsx
+++ b/downloads/en/proximite-revues.xlsx
@@ -458,7 +458,7 @@
         <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -466,10 +466,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         <v>57</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -488,10 +488,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
